--- a/0.EJEMPLOS_EXAMPLES/FastTest PlugIn - DataBase_Examples - English.xlsx
+++ b/0.EJEMPLOS_EXAMPLES/FastTest PlugIn - DataBase_Examples - English.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milag\Desktop\FTP_81\0.EJEMPLOS_EXAMPLES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\0.EJEMPLOS_EXAMPLES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44935B7-5ADB-466E-9F99-F9D48E8DE430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA995536-FA24-4D42-A70B-81EB9A6C6475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3194,9 +3194,6 @@
 默认情况下，根据您要使用的语言编写相应的数字。 您可以随时更改它。</t>
   </si>
   <si>
-    <t>V - 7.8  - 02/04/2023</t>
-  </si>
-  <si>
     <t>Attention to reading</t>
   </si>
   <si>
@@ -3245,21 +3242,6 @@
     <t>m</t>
   </si>
   <si>
-    <t>m^{^2^}^</t>
-  </si>
-  <si>
-    <t>m^{^3^}^</t>
-  </si>
-  <si>
-    <t>m^{^4^}^</t>
-  </si>
-  <si>
-    <t>m_{_2_}_</t>
-  </si>
-  <si>
-    <t>m_{_3_}_</t>
-  </si>
-  <si>
     <t>Math</t>
   </si>
   <si>
@@ -3279,12 +3261,6 @@
   </si>
   <si>
     <t>mm</t>
-  </si>
-  <si>
-    <t>mm^{^2^}^</t>
-  </si>
-  <si>
-    <t>mm^{^3^}^</t>
   </si>
   <si>
     <t>Santiago's WHITE horse is white</t>
@@ -3633,6 +3609,30 @@
   <si>
     <t>Select the correct formula: &lt;br&gt;
 {1:MCHS:~%100%\(\frac{\cos^2(x)\}{x-1\}\)#~%0%\(-\frac{\cos^2(x)\}{x-1\}\)#}&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>V - 8.3  - 02/01/2025</t>
+  </si>
+  <si>
+    <t>m²</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>m⁴</t>
+  </si>
+  <si>
+    <t>m₂</t>
+  </si>
+  <si>
+    <t>m₃</t>
+  </si>
+  <si>
+    <t>mm³</t>
+  </si>
+  <si>
+    <t>mm²</t>
   </si>
 </sst>
 </file>
@@ -4491,7 +4491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5262,6 +5262,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5364,7 +5368,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="348">
@@ -21673,7 +21677,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja_00"/>
   <dimension ref="A1:T47"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.64453125" customWidth="1"/>
     <col min="2" max="2" width="2.64453125" customWidth="1"/>
@@ -21683,32 +21687,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.7" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="262" t="s">
+      <c r="A1" s="263" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="252" t="s">
+      <c r="B1" s="253" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="253"/>
-      <c r="O1" s="253"/>
-      <c r="P1" s="253"/>
-      <c r="Q1" s="253"/>
-      <c r="R1" s="253"/>
-      <c r="S1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="254"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="255"/>
     </row>
     <row r="2" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="263"/>
+      <c r="A2" s="264"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -21729,23 +21733,23 @@
       <c r="S2" s="6"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A3" s="263"/>
+      <c r="A3" s="264"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="269" t="str">
+      <c r="G3" s="270" t="str">
         <f ca="1">INDIRECT("Z_IN_04_"&amp;IDIOMA)</f>
         <v>This Application has been developed, in the first version, by:</v>
       </c>
-      <c r="H3" s="269"/>
-      <c r="I3" s="269"/>
-      <c r="J3" s="269"/>
-      <c r="K3" s="269"/>
-      <c r="L3" s="269"/>
-      <c r="M3" s="269"/>
-      <c r="N3" s="269"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="270"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -21753,7 +21757,7 @@
       <c r="S3" s="6"/>
     </row>
     <row r="4" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="263"/>
+      <c r="A4" s="264"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -21774,125 +21778,125 @@
       <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="263"/>
+      <c r="A5" s="264"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="261"/>
       <c r="H5" s="134"/>
-      <c r="I5" s="270" t="s">
+      <c r="I5" s="271" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="244"/>
-      <c r="O5" s="244"/>
-      <c r="P5" s="261" t="s">
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="262" t="s">
         <v>651</v>
       </c>
-      <c r="Q5" s="261"/>
-      <c r="R5" s="261"/>
+      <c r="Q5" s="262"/>
+      <c r="R5" s="262"/>
       <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="263"/>
+      <c r="A6" s="264"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
       <c r="H6" s="134"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-      <c r="P6" s="272" t="str">
+      <c r="N6" s="245"/>
+      <c r="O6" s="245"/>
+      <c r="P6" s="273" t="str">
         <f ca="1">INDIRECT("Z_IN_01_"&amp;IDIOMA)</f>
         <v>YOUTUBE CHANNEL</v>
       </c>
-      <c r="Q6" s="272"/>
-      <c r="R6" s="272"/>
+      <c r="Q6" s="273"/>
+      <c r="R6" s="273"/>
       <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="263"/>
+      <c r="A7" s="264"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="260"/>
-      <c r="G7" s="260"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="261"/>
       <c r="H7" s="134"/>
-      <c r="I7" s="269" t="str">
+      <c r="I7" s="270" t="str">
         <f ca="1">INDIRECT("Z_IN_05_"&amp;IDIOMA)</f>
         <v>Cadiz University</v>
       </c>
-      <c r="J7" s="269"/>
-      <c r="K7" s="269"/>
-      <c r="L7" s="269"/>
+      <c r="J7" s="270"/>
+      <c r="K7" s="270"/>
+      <c r="L7" s="270"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="272"/>
-      <c r="Q7" s="272"/>
-      <c r="R7" s="272"/>
+      <c r="N7" s="245"/>
+      <c r="O7" s="245"/>
+      <c r="P7" s="273"/>
+      <c r="Q7" s="273"/>
+      <c r="R7" s="273"/>
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="263"/>
+      <c r="A8" s="264"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
+      <c r="F8" s="261"/>
+      <c r="G8" s="261"/>
       <c r="H8" s="134"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
+      <c r="N8" s="245"/>
+      <c r="O8" s="245"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="264"/>
+      <c r="A9" s="265"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="255" t="str">
+      <c r="C9" s="256" t="str">
         <f ca="1">INDIRECT("Z_IN_03_"&amp;IDIOMA)</f>
         <v>READ CAREFULLY</v>
       </c>
-      <c r="D9" s="255"/>
+      <c r="D9" s="256"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="261"/>
       <c r="H9" s="134"/>
-      <c r="I9" s="271" t="s">
+      <c r="I9" s="272" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="271"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="271"/>
+      <c r="J9" s="272"/>
+      <c r="K9" s="272"/>
+      <c r="L9" s="272"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="244"/>
-      <c r="O9" s="244"/>
-      <c r="P9" s="273" t="s">
-        <v>831</v>
-      </c>
-      <c r="Q9" s="273"/>
-      <c r="R9" s="273"/>
+      <c r="N9" s="245"/>
+      <c r="O9" s="245"/>
+      <c r="P9" s="274" t="s">
+        <v>968</v>
+      </c>
+      <c r="Q9" s="274"/>
+      <c r="R9" s="274"/>
       <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
@@ -21900,256 +21904,256 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
       <c r="H10" s="134"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="244"/>
-      <c r="O10" s="244"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="6"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="265" t="s">
+      <c r="A11" s="266" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="256" t="str">
+      <c r="D11" s="257" t="str">
         <f ca="1">INDIRECT("Z_IN_06_"&amp;IDIOMA)</f>
         <v>1. This application has been developed thanks to a Teaching Innovation Project approved by the Teaching Innovation Unit of the University of Cádiz.
 2. The end user is the teacher who wants to use the QUESTIONNAIRES of the Moodle platform. It can also be used by anyone who wants to have their Question Banks stored in one place and in order.
 3. The application serves to facilitate the creation of a BANK OF QUESTIONS for the questionnaires, the end user must check that the questions are imported correctly (at least the first times) as well as if they have filled in the data appropriately, as if was doing in Moodle.
 Click on the TYPE OF QUESTION on which you want to CONSULT the stored questions.</v>
       </c>
-      <c r="E11" s="256"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="256"/>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
-      <c r="M11" s="256"/>
-      <c r="N11" s="256"/>
-      <c r="O11" s="256"/>
-      <c r="P11" s="256"/>
-      <c r="Q11" s="256"/>
-      <c r="R11" s="256"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
+      <c r="M11" s="257"/>
+      <c r="N11" s="257"/>
+      <c r="O11" s="257"/>
+      <c r="P11" s="257"/>
+      <c r="Q11" s="257"/>
+      <c r="R11" s="257"/>
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="265"/>
+      <c r="A12" s="266"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="256"/>
-      <c r="E12" s="256"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="256"/>
-      <c r="H12" s="256"/>
-      <c r="I12" s="256"/>
-      <c r="J12" s="256"/>
-      <c r="K12" s="256"/>
-      <c r="L12" s="256"/>
-      <c r="M12" s="256"/>
-      <c r="N12" s="256"/>
-      <c r="O12" s="256"/>
-      <c r="P12" s="256"/>
-      <c r="Q12" s="256"/>
-      <c r="R12" s="256"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="257"/>
+      <c r="F12" s="257"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="257"/>
+      <c r="I12" s="257"/>
+      <c r="J12" s="257"/>
+      <c r="K12" s="257"/>
+      <c r="L12" s="257"/>
+      <c r="M12" s="257"/>
+      <c r="N12" s="257"/>
+      <c r="O12" s="257"/>
+      <c r="P12" s="257"/>
+      <c r="Q12" s="257"/>
+      <c r="R12" s="257"/>
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A13" s="265"/>
+      <c r="A13" s="266"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="256"/>
-      <c r="E13" s="256"/>
-      <c r="F13" s="256"/>
-      <c r="G13" s="256"/>
-      <c r="H13" s="256"/>
-      <c r="I13" s="256"/>
-      <c r="J13" s="256"/>
-      <c r="K13" s="256"/>
-      <c r="L13" s="256"/>
-      <c r="M13" s="256"/>
-      <c r="N13" s="256"/>
-      <c r="O13" s="256"/>
-      <c r="P13" s="256"/>
-      <c r="Q13" s="256"/>
-      <c r="R13" s="256"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
+      <c r="F13" s="257"/>
+      <c r="G13" s="257"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="257"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="257"/>
+      <c r="M13" s="257"/>
+      <c r="N13" s="257"/>
+      <c r="O13" s="257"/>
+      <c r="P13" s="257"/>
+      <c r="Q13" s="257"/>
+      <c r="R13" s="257"/>
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="256"/>
-      <c r="E14" s="256"/>
-      <c r="F14" s="256"/>
-      <c r="G14" s="256"/>
-      <c r="H14" s="256"/>
-      <c r="I14" s="256"/>
-      <c r="J14" s="256"/>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="256"/>
-      <c r="N14" s="256"/>
-      <c r="O14" s="256"/>
-      <c r="P14" s="256"/>
-      <c r="Q14" s="256"/>
-      <c r="R14" s="256"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="257"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="257"/>
+      <c r="J14" s="257"/>
+      <c r="K14" s="257"/>
+      <c r="L14" s="257"/>
+      <c r="M14" s="257"/>
+      <c r="N14" s="257"/>
+      <c r="O14" s="257"/>
+      <c r="P14" s="257"/>
+      <c r="Q14" s="257"/>
+      <c r="R14" s="257"/>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="256"/>
-      <c r="E15" s="256"/>
-      <c r="F15" s="256"/>
-      <c r="G15" s="256"/>
-      <c r="H15" s="256"/>
-      <c r="I15" s="256"/>
-      <c r="J15" s="256"/>
-      <c r="K15" s="256"/>
-      <c r="L15" s="256"/>
-      <c r="M15" s="256"/>
-      <c r="N15" s="256"/>
-      <c r="O15" s="256"/>
-      <c r="P15" s="256"/>
-      <c r="Q15" s="256"/>
-      <c r="R15" s="256"/>
+      <c r="D15" s="257"/>
+      <c r="E15" s="257"/>
+      <c r="F15" s="257"/>
+      <c r="G15" s="257"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="257"/>
+      <c r="J15" s="257"/>
+      <c r="K15" s="257"/>
+      <c r="L15" s="257"/>
+      <c r="M15" s="257"/>
+      <c r="N15" s="257"/>
+      <c r="O15" s="257"/>
+      <c r="P15" s="257"/>
+      <c r="Q15" s="257"/>
+      <c r="R15" s="257"/>
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="256"/>
-      <c r="E16" s="256"/>
-      <c r="F16" s="256"/>
-      <c r="G16" s="256"/>
-      <c r="H16" s="256"/>
-      <c r="I16" s="256"/>
-      <c r="J16" s="256"/>
-      <c r="K16" s="256"/>
-      <c r="L16" s="256"/>
-      <c r="M16" s="256"/>
-      <c r="N16" s="256"/>
-      <c r="O16" s="256"/>
-      <c r="P16" s="256"/>
-      <c r="Q16" s="256"/>
-      <c r="R16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="257"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
+      <c r="M16" s="257"/>
+      <c r="N16" s="257"/>
+      <c r="O16" s="257"/>
+      <c r="P16" s="257"/>
+      <c r="Q16" s="257"/>
+      <c r="R16" s="257"/>
       <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A17" s="266" t="str">
+      <c r="A17" s="267" t="str">
         <f>IFERROR(HLOOKUP(LANGUAGE,DICCIONARIO!F1:K20,20,0),LANGUAGE)</f>
         <v>CUSTOM DICTIONARY</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="256"/>
-      <c r="E17" s="256"/>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
-      <c r="J17" s="256"/>
-      <c r="K17" s="256"/>
-      <c r="L17" s="256"/>
-      <c r="M17" s="256"/>
-      <c r="N17" s="256"/>
-      <c r="O17" s="256"/>
-      <c r="P17" s="256"/>
-      <c r="Q17" s="256"/>
-      <c r="R17" s="256"/>
+      <c r="D17" s="257"/>
+      <c r="E17" s="257"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
+      <c r="J17" s="257"/>
+      <c r="K17" s="257"/>
+      <c r="L17" s="257"/>
+      <c r="M17" s="257"/>
+      <c r="N17" s="257"/>
+      <c r="O17" s="257"/>
+      <c r="P17" s="257"/>
+      <c r="Q17" s="257"/>
+      <c r="R17" s="257"/>
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="266"/>
+      <c r="A18" s="267"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="256"/>
-      <c r="E18" s="256"/>
-      <c r="F18" s="256"/>
-      <c r="G18" s="256"/>
-      <c r="H18" s="256"/>
-      <c r="I18" s="256"/>
-      <c r="J18" s="256"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="256"/>
-      <c r="M18" s="256"/>
-      <c r="N18" s="256"/>
-      <c r="O18" s="256"/>
-      <c r="P18" s="256"/>
-      <c r="Q18" s="256"/>
-      <c r="R18" s="256"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
+      <c r="M18" s="257"/>
+      <c r="N18" s="257"/>
+      <c r="O18" s="257"/>
+      <c r="P18" s="257"/>
+      <c r="Q18" s="257"/>
+      <c r="R18" s="257"/>
       <c r="S18" s="6"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A19" s="266"/>
+      <c r="A19" s="267"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="256"/>
-      <c r="E19" s="256"/>
-      <c r="F19" s="256"/>
-      <c r="G19" s="256"/>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
-      <c r="M19" s="256"/>
-      <c r="N19" s="256"/>
-      <c r="O19" s="256"/>
-      <c r="P19" s="256"/>
-      <c r="Q19" s="256"/>
-      <c r="R19" s="256"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="257"/>
+      <c r="J19" s="257"/>
+      <c r="K19" s="257"/>
+      <c r="L19" s="257"/>
+      <c r="M19" s="257"/>
+      <c r="N19" s="257"/>
+      <c r="O19" s="257"/>
+      <c r="P19" s="257"/>
+      <c r="Q19" s="257"/>
+      <c r="R19" s="257"/>
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="256"/>
-      <c r="E20" s="256"/>
-      <c r="F20" s="256"/>
-      <c r="G20" s="256"/>
-      <c r="H20" s="256"/>
-      <c r="I20" s="256"/>
-      <c r="J20" s="256"/>
-      <c r="K20" s="256"/>
-      <c r="L20" s="256"/>
-      <c r="M20" s="256"/>
-      <c r="N20" s="256"/>
-      <c r="O20" s="256"/>
-      <c r="P20" s="256"/>
-      <c r="Q20" s="256"/>
-      <c r="R20" s="256"/>
+      <c r="D20" s="257"/>
+      <c r="E20" s="257"/>
+      <c r="F20" s="257"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="257"/>
+      <c r="I20" s="257"/>
+      <c r="J20" s="257"/>
+      <c r="K20" s="257"/>
+      <c r="L20" s="257"/>
+      <c r="M20" s="257"/>
+      <c r="N20" s="257"/>
+      <c r="O20" s="257"/>
+      <c r="P20" s="257"/>
+      <c r="Q20" s="257"/>
+      <c r="R20" s="257"/>
       <c r="S20" s="6"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="256"/>
-      <c r="E21" s="256"/>
-      <c r="F21" s="256"/>
-      <c r="G21" s="256"/>
-      <c r="H21" s="256"/>
-      <c r="I21" s="256"/>
-      <c r="J21" s="256"/>
-      <c r="K21" s="256"/>
-      <c r="L21" s="256"/>
-      <c r="M21" s="256"/>
-      <c r="N21" s="256"/>
-      <c r="O21" s="256"/>
-      <c r="P21" s="256"/>
-      <c r="Q21" s="256"/>
-      <c r="R21" s="256"/>
+      <c r="D21" s="257"/>
+      <c r="E21" s="257"/>
+      <c r="F21" s="257"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="257"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="257"/>
+      <c r="L21" s="257"/>
+      <c r="M21" s="257"/>
+      <c r="N21" s="257"/>
+      <c r="O21" s="257"/>
+      <c r="P21" s="257"/>
+      <c r="Q21" s="257"/>
+      <c r="R21" s="257"/>
       <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22174,172 +22178,172 @@
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="4"/>
-      <c r="C23" s="257" t="str">
+      <c r="C23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_10_"&amp;IDIOMA)</f>
         <v>MC 1A</v>
       </c>
-      <c r="D23" s="258"/>
-      <c r="E23" s="257" t="str">
+      <c r="D23" s="259"/>
+      <c r="E23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_11_"&amp;IDIOMA)</f>
         <v>MC +A</v>
       </c>
-      <c r="F23" s="259"/>
-      <c r="G23" s="257" t="str">
+      <c r="F23" s="260"/>
+      <c r="G23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_12_"&amp;IDIOMA)</f>
         <v>TF</v>
       </c>
-      <c r="H23" s="259"/>
-      <c r="I23" s="257" t="str">
+      <c r="H23" s="260"/>
+      <c r="I23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_13_"&amp;IDIOMA)</f>
         <v>MA</v>
       </c>
-      <c r="J23" s="258"/>
-      <c r="K23" s="257" t="str">
+      <c r="J23" s="259"/>
+      <c r="K23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_14_"&amp;IDIOMA)</f>
         <v>SA</v>
       </c>
-      <c r="L23" s="259"/>
-      <c r="M23" s="257" t="str">
+      <c r="L23" s="260"/>
+      <c r="M23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_15_"&amp;IDIOMA)</f>
         <v>MW</v>
       </c>
-      <c r="N23" s="259"/>
-      <c r="O23" s="257" t="str">
+      <c r="N23" s="260"/>
+      <c r="O23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_31_"&amp;IDIOMA)</f>
         <v>ES</v>
       </c>
-      <c r="P23" s="259"/>
-      <c r="Q23" s="257" t="str">
+      <c r="P23" s="260"/>
+      <c r="Q23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_16_"&amp;IDIOMA)</f>
         <v>CL</v>
       </c>
-      <c r="R23" s="259"/>
+      <c r="R23" s="260"/>
       <c r="S23" s="6"/>
     </row>
     <row r="24" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="4"/>
-      <c r="C24" s="248" t="str">
+      <c r="C24" s="249" t="str">
         <f ca="1">INDIRECT("Z_IN_08_"&amp;IDIOMA)</f>
         <v>Multiple Choice 1A</v>
       </c>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249" t="str">
+      <c r="D24" s="250"/>
+      <c r="E24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_09_"&amp;IDIOMA)</f>
         <v>Multiple Choice +A</v>
       </c>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249" t="str">
+      <c r="F24" s="250"/>
+      <c r="G24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_10_"&amp;IDIOMA)</f>
         <v>True/False</v>
       </c>
-      <c r="H24" s="249"/>
-      <c r="I24" s="249" t="str">
+      <c r="H24" s="250"/>
+      <c r="I24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_11_"&amp;IDIOMA)</f>
         <v>Matching</v>
       </c>
-      <c r="J24" s="249"/>
-      <c r="K24" s="249" t="str">
+      <c r="J24" s="250"/>
+      <c r="K24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_12_"&amp;IDIOMA)</f>
         <v>Short Answer</v>
       </c>
-      <c r="L24" s="249"/>
-      <c r="M24" s="249" t="str">
+      <c r="L24" s="250"/>
+      <c r="M24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_13_"&amp;IDIOMA)</f>
         <v>Missing Word</v>
       </c>
-      <c r="N24" s="249"/>
-      <c r="O24" s="249" t="str">
+      <c r="N24" s="250"/>
+      <c r="O24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_16_"&amp;IDIOMA)</f>
         <v>Essay</v>
       </c>
-      <c r="P24" s="249"/>
-      <c r="Q24" s="249" t="str">
+      <c r="P24" s="250"/>
+      <c r="Q24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_14_"&amp;IDIOMA)</f>
         <v>Cloze</v>
       </c>
-      <c r="R24" s="274"/>
+      <c r="R24" s="275"/>
       <c r="S24" s="6"/>
     </row>
     <row r="25" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="4"/>
-      <c r="C25" s="250"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="251"/>
-      <c r="H25" s="251"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
-      <c r="M25" s="251"/>
-      <c r="N25" s="251"/>
-      <c r="O25" s="251"/>
-      <c r="P25" s="251"/>
-      <c r="Q25" s="251"/>
-      <c r="R25" s="275"/>
+      <c r="C25" s="251"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
+      <c r="M25" s="252"/>
+      <c r="N25" s="252"/>
+      <c r="O25" s="252"/>
+      <c r="P25" s="252"/>
+      <c r="Q25" s="252"/>
+      <c r="R25" s="276"/>
       <c r="S25" s="6"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="4"/>
-      <c r="C26" s="245" t="str">
+      <c r="C26" s="246" t="str">
         <f ca="1">'Datos OM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Questions</v>
       </c>
-      <c r="D26" s="247"/>
-      <c r="E26" s="245" t="str">
+      <c r="D26" s="248"/>
+      <c r="E26" s="246" t="str">
         <f ca="1">'Datos O2'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Questions</v>
       </c>
-      <c r="F26" s="246"/>
-      <c r="G26" s="245" t="str">
+      <c r="F26" s="247"/>
+      <c r="G26" s="246" t="str">
         <f ca="1">'Datos VF'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Questions</v>
       </c>
-      <c r="H26" s="246"/>
-      <c r="I26" s="245" t="str">
+      <c r="H26" s="247"/>
+      <c r="I26" s="246" t="str">
         <f ca="1">'Datos EM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Questions</v>
       </c>
-      <c r="J26" s="247"/>
-      <c r="K26" s="245" t="str">
+      <c r="J26" s="248"/>
+      <c r="K26" s="246" t="str">
         <f ca="1">'Datos RC'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Questions</v>
       </c>
-      <c r="L26" s="246"/>
-      <c r="M26" s="245" t="str">
+      <c r="L26" s="247"/>
+      <c r="M26" s="246" t="str">
         <f ca="1">'Datos PP'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Questions</v>
       </c>
-      <c r="N26" s="246"/>
-      <c r="O26" s="245" t="str">
+      <c r="N26" s="247"/>
+      <c r="O26" s="246" t="str">
         <f ca="1">'Datos EN'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Questions</v>
       </c>
-      <c r="P26" s="246"/>
-      <c r="Q26" s="245" t="str">
+      <c r="P26" s="247"/>
+      <c r="Q26" s="246" t="str">
         <f ca="1">'Datos CL'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Questions</v>
       </c>
-      <c r="R26" s="246"/>
+      <c r="R26" s="247"/>
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="267" t="str">
+      <c r="D27" s="268" t="str">
         <f ca="1">INDIRECT("Z_IN_07_"&amp;IDIOMA)</f>
         <v>This SHEET is used to store the questions and to be able to reuse them when necessary, without having to retype them for a new BANK OF QUESTIONS.</v>
       </c>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="267"/>
-      <c r="K27" s="267"/>
-      <c r="L27" s="267"/>
-      <c r="M27" s="267"/>
+      <c r="E27" s="268"/>
+      <c r="F27" s="268"/>
+      <c r="G27" s="268"/>
+      <c r="H27" s="268"/>
+      <c r="I27" s="268"/>
+      <c r="J27" s="268"/>
+      <c r="K27" s="268"/>
+      <c r="L27" s="268"/>
+      <c r="M27" s="268"/>
       <c r="N27" s="144"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
@@ -22350,141 +22354,141 @@
     <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="268"/>
-      <c r="E28" s="268"/>
-      <c r="F28" s="268"/>
-      <c r="G28" s="268"/>
-      <c r="H28" s="268"/>
-      <c r="I28" s="268"/>
-      <c r="J28" s="268"/>
-      <c r="K28" s="268"/>
-      <c r="L28" s="268"/>
-      <c r="M28" s="268"/>
+      <c r="D28" s="269"/>
+      <c r="E28" s="269"/>
+      <c r="F28" s="269"/>
+      <c r="G28" s="269"/>
+      <c r="H28" s="269"/>
+      <c r="I28" s="269"/>
+      <c r="J28" s="269"/>
+      <c r="K28" s="269"/>
+      <c r="L28" s="269"/>
+      <c r="M28" s="269"/>
       <c r="N28" s="145"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="244"/>
-      <c r="Q28" s="244"/>
-      <c r="R28" s="244"/>
+      <c r="P28" s="245"/>
+      <c r="Q28" s="245"/>
+      <c r="R28" s="245"/>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="268"/>
-      <c r="E29" s="268"/>
-      <c r="F29" s="268"/>
-      <c r="G29" s="268"/>
-      <c r="H29" s="268"/>
-      <c r="I29" s="268"/>
-      <c r="J29" s="268"/>
-      <c r="K29" s="268"/>
-      <c r="L29" s="268"/>
-      <c r="M29" s="268"/>
+      <c r="D29" s="269"/>
+      <c r="E29" s="269"/>
+      <c r="F29" s="269"/>
+      <c r="G29" s="269"/>
+      <c r="H29" s="269"/>
+      <c r="I29" s="269"/>
+      <c r="J29" s="269"/>
+      <c r="K29" s="269"/>
+      <c r="L29" s="269"/>
+      <c r="M29" s="269"/>
       <c r="N29" s="145"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="244"/>
-      <c r="Q29" s="244"/>
-      <c r="R29" s="244"/>
+      <c r="P29" s="245"/>
+      <c r="Q29" s="245"/>
+      <c r="R29" s="245"/>
       <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="268"/>
-      <c r="E30" s="268"/>
-      <c r="F30" s="268"/>
-      <c r="G30" s="268"/>
-      <c r="H30" s="268"/>
-      <c r="I30" s="268"/>
-      <c r="J30" s="268"/>
-      <c r="K30" s="268"/>
-      <c r="L30" s="268"/>
-      <c r="M30" s="268"/>
+      <c r="D30" s="269"/>
+      <c r="E30" s="269"/>
+      <c r="F30" s="269"/>
+      <c r="G30" s="269"/>
+      <c r="H30" s="269"/>
+      <c r="I30" s="269"/>
+      <c r="J30" s="269"/>
+      <c r="K30" s="269"/>
+      <c r="L30" s="269"/>
+      <c r="M30" s="269"/>
       <c r="N30" s="145"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="244"/>
-      <c r="Q30" s="244"/>
-      <c r="R30" s="244"/>
+      <c r="P30" s="245"/>
+      <c r="Q30" s="245"/>
+      <c r="R30" s="245"/>
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="268"/>
-      <c r="E31" s="268"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="268"/>
-      <c r="H31" s="268"/>
-      <c r="I31" s="268"/>
-      <c r="J31" s="268"/>
-      <c r="K31" s="268"/>
-      <c r="L31" s="268"/>
-      <c r="M31" s="268"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="269"/>
+      <c r="L31" s="269"/>
+      <c r="M31" s="269"/>
       <c r="N31" s="145"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="244"/>
-      <c r="Q31" s="244"/>
-      <c r="R31" s="244"/>
+      <c r="P31" s="245"/>
+      <c r="Q31" s="245"/>
+      <c r="R31" s="245"/>
       <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="268"/>
-      <c r="E32" s="268"/>
-      <c r="F32" s="268"/>
-      <c r="G32" s="268"/>
-      <c r="H32" s="268"/>
-      <c r="I32" s="268"/>
-      <c r="J32" s="268"/>
-      <c r="K32" s="268"/>
-      <c r="L32" s="268"/>
-      <c r="M32" s="268"/>
+      <c r="D32" s="269"/>
+      <c r="E32" s="269"/>
+      <c r="F32" s="269"/>
+      <c r="G32" s="269"/>
+      <c r="H32" s="269"/>
+      <c r="I32" s="269"/>
+      <c r="J32" s="269"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="269"/>
+      <c r="M32" s="269"/>
       <c r="N32" s="145"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="244"/>
-      <c r="Q32" s="244"/>
-      <c r="R32" s="244"/>
+      <c r="P32" s="245"/>
+      <c r="Q32" s="245"/>
+      <c r="R32" s="245"/>
       <c r="S32" s="6"/>
     </row>
     <row r="33" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="268"/>
-      <c r="E33" s="268"/>
-      <c r="F33" s="268"/>
-      <c r="G33" s="268"/>
-      <c r="H33" s="268"/>
-      <c r="I33" s="268"/>
-      <c r="J33" s="268"/>
-      <c r="K33" s="268"/>
-      <c r="L33" s="268"/>
-      <c r="M33" s="268"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="269"/>
+      <c r="G33" s="269"/>
+      <c r="H33" s="269"/>
+      <c r="I33" s="269"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="269"/>
+      <c r="L33" s="269"/>
+      <c r="M33" s="269"/>
       <c r="N33" s="145"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="244"/>
-      <c r="Q33" s="244"/>
-      <c r="R33" s="244"/>
+      <c r="P33" s="245"/>
+      <c r="Q33" s="245"/>
+      <c r="R33" s="245"/>
       <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="268"/>
-      <c r="E34" s="268"/>
-      <c r="F34" s="268"/>
-      <c r="G34" s="268"/>
-      <c r="H34" s="268"/>
-      <c r="I34" s="268"/>
-      <c r="J34" s="268"/>
-      <c r="K34" s="268"/>
-      <c r="L34" s="268"/>
-      <c r="M34" s="268"/>
+      <c r="D34" s="269"/>
+      <c r="E34" s="269"/>
+      <c r="F34" s="269"/>
+      <c r="G34" s="269"/>
+      <c r="H34" s="269"/>
+      <c r="I34" s="269"/>
+      <c r="J34" s="269"/>
+      <c r="K34" s="269"/>
+      <c r="L34" s="269"/>
+      <c r="M34" s="269"/>
       <c r="N34" s="145"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="244"/>
-      <c r="Q34" s="244"/>
-      <c r="R34" s="244"/>
+      <c r="P34" s="245"/>
+      <c r="Q34" s="245"/>
+      <c r="R34" s="245"/>
       <c r="S34" s="6"/>
     </row>
     <row r="35" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22599,7 +22603,7 @@
     </row>
     <row r="47" spans="1:19" ht="5.0999999999999996" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="B4ZtyPI8lv6/MGOS3+9a5fUlVKn8W7m5tc5qom7GwcpKDO4mxFaT3Eq647jn8+lsT+zoaLPf06hAUqFkuo98DA==" saltValue="Oavj1BI2LOGiAwJ94csGEA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="acAn9ihr6ItOVHZ2Lb01+IR6mRyZkiG43hEXwr5k1sANkhSxd7Zx0ZrDIk/OzCW2ivQO4VfxGCT/f/SayuA7iQ==" saltValue="FEByDVRCBUO6SJgORjRgCA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="42">
     <mergeCell ref="A1:A9"/>
     <mergeCell ref="A11:A13"/>
@@ -22667,7 +22671,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Hoja_50"/>
   <dimension ref="A1:BF382"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.64453125" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="2" max="3" width="6" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -27822,7 +27826,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja_21"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -27906,7 +27910,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!C24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - MULTIPLE CHOICE 1A
+        <v>FastTest PlugIn - V8.3  - MULTIPLE CHOICE 1A
 Question statement</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28125,46 +28129,46 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>831</v>
+      </c>
+      <c r="F5" s="76" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="G5" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>835</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>837</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="L5" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="M5" s="24" t="s">
         <v>838</v>
       </c>
-      <c r="L5" s="17" t="s">
-        <v>836</v>
-      </c>
-      <c r="M5" s="24" t="s">
+      <c r="N5" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="O5" s="26" t="s">
         <v>840</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="P5" s="27" t="s">
         <v>841</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="Q5" s="28" t="s">
         <v>842</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="R5" s="29" t="s">
         <v>843</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>844</v>
       </c>
       <c r="S5" s="24">
         <v>100</v>
@@ -28207,46 +28211,46 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
+        <v>844</v>
+      </c>
+      <c r="F6" s="76" t="s">
         <v>845</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="G6" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>847</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>848</v>
+        <v>969</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>849</v>
+        <v>970</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>850</v>
+        <v>971</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>851</v>
+        <v>972</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>852</v>
+        <v>973</v>
       </c>
       <c r="M6" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="N6" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="O6" s="26" t="s">
         <v>840</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="P6" s="27" t="s">
         <v>841</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="Q6" s="28" t="s">
         <v>842</v>
       </c>
-      <c r="Q6" s="28" t="s">
+      <c r="R6" s="29" t="s">
         <v>843</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>844</v>
       </c>
       <c r="S6" s="24">
         <v>100</v>
@@ -28279,31 +28283,31 @@
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="16"/>
       <c r="L7" s="17"/>
       <c r="M7" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="N7" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="O7" s="26" t="s">
         <v>840</v>
-      </c>
-      <c r="O7" s="26" t="s">
-        <v>841</v>
       </c>
       <c r="P7" s="27"/>
       <c r="Q7" s="28"/>
@@ -28343,7 +28347,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja_22"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -28427,7 +28431,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!E24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - MULTIPLE CHOICE +A
+        <v>FastTest PlugIn - V8.3  - MULTIPLE CHOICE +A
 Question statement</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28650,46 +28654,46 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>831</v>
+      </c>
+      <c r="F5" s="76" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="G5" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>834</v>
-      </c>
       <c r="H5" s="13" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="I5" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>837</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="L5" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="M5" s="24" t="s">
         <v>838</v>
       </c>
-      <c r="L5" s="17" t="s">
-        <v>836</v>
-      </c>
-      <c r="M5" s="24" t="s">
+      <c r="N5" s="25" t="s">
+        <v>838</v>
+      </c>
+      <c r="O5" s="26" t="s">
         <v>839</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="P5" s="27" t="s">
         <v>839</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="Q5" s="28" t="s">
         <v>840</v>
       </c>
-      <c r="P5" s="27" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q5" s="28" t="s">
+      <c r="R5" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="S5" s="24">
         <v>50</v>
@@ -28701,7 +28705,9 @@
       <c r="V5" s="27"/>
       <c r="W5" s="28"/>
       <c r="X5" s="29"/>
-      <c r="Y5" s="199"/>
+      <c r="Y5" s="199">
+        <v>2</v>
+      </c>
       <c r="Z5" s="29"/>
       <c r="AA5" s="29"/>
       <c r="AB5" s="29"/>
@@ -28724,46 +28730,46 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
+        <v>844</v>
+      </c>
+      <c r="F6" s="151" t="s">
         <v>845</v>
       </c>
-      <c r="F6" s="151" t="s">
+      <c r="G6" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>847</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>848</v>
+        <v>972</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>849</v>
+        <v>970</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>860</v>
+        <v>974</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>861</v>
+        <v>975</v>
       </c>
       <c r="M6" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>838</v>
+      </c>
+      <c r="O6" s="26" t="s">
         <v>839</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="P6" s="27" t="s">
         <v>839</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="Q6" s="28" t="s">
         <v>840</v>
       </c>
-      <c r="P6" s="27" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q6" s="28" t="s">
+      <c r="R6" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="S6" s="24">
         <v>50</v>
@@ -28801,7 +28807,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Hoja_23"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -28878,7 +28884,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!G24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - TRUE/FALSE
+        <v>FastTest PlugIn - V8.3  - TRUE/FALSE
 Question statement</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -29047,25 +29053,25 @@
       <c r="B5" s="172"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>862</v>
-      </c>
-      <c r="G5" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="G5" s="244" t="s">
         <v>189</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="L5" s="29"/>
       <c r="M5" s="24"/>
@@ -29087,16 +29093,16 @@
       <c r="AC5" s="29"/>
       <c r="AD5" s="29"/>
       <c r="AE5" s="30" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="AI5" s="66"/>
     </row>
@@ -29105,22 +29111,22 @@
       <c r="B6" s="172"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>871</v>
-      </c>
-      <c r="G6" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="G6" s="244" t="s">
         <v>196</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="K6" s="28"/>
       <c r="L6" s="29"/>
@@ -29143,16 +29149,16 @@
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="30" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AF6" s="31" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AG6" s="32" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="AI6" s="66"/>
     </row>
@@ -29170,7 +29176,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja_24"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -29251,7 +29257,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!I24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - MATCHING
+        <v>FastTest PlugIn - V8.3  - MATCHING
 Question statement</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -29486,94 +29492,94 @@
       <c r="B5" s="173"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>866</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>867</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>868</v>
+      </c>
+      <c r="H5" s="87" t="s">
+        <v>869</v>
+      </c>
+      <c r="I5" s="88" t="s">
+        <v>870</v>
+      </c>
+      <c r="J5" s="88" t="s">
+        <v>871</v>
+      </c>
+      <c r="K5" s="89" t="s">
+        <v>872</v>
+      </c>
+      <c r="L5" s="89" t="s">
+        <v>873</v>
+      </c>
+      <c r="M5" s="90" t="s">
         <v>874</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="N5" s="90" t="s">
         <v>875</v>
       </c>
-      <c r="G5" s="87" t="s">
+      <c r="O5" s="91" t="s">
         <v>876</v>
       </c>
-      <c r="H5" s="87" t="s">
+      <c r="P5" s="91" t="s">
         <v>877</v>
       </c>
-      <c r="I5" s="88" t="s">
+      <c r="Q5" s="92" t="s">
         <v>878</v>
       </c>
-      <c r="J5" s="88" t="s">
+      <c r="R5" s="92" t="s">
         <v>879</v>
       </c>
-      <c r="K5" s="89" t="s">
+      <c r="S5" s="87" t="s">
         <v>880</v>
       </c>
-      <c r="L5" s="89" t="s">
+      <c r="T5" s="87" t="s">
         <v>881</v>
       </c>
-      <c r="M5" s="90" t="s">
+      <c r="U5" s="88" t="s">
         <v>882</v>
       </c>
-      <c r="N5" s="90" t="s">
+      <c r="V5" s="88" t="s">
         <v>883</v>
       </c>
-      <c r="O5" s="91" t="s">
+      <c r="W5" s="89" t="s">
         <v>884</v>
       </c>
-      <c r="P5" s="91" t="s">
+      <c r="X5" s="89" t="s">
         <v>885</v>
       </c>
-      <c r="Q5" s="92" t="s">
+      <c r="Y5" s="90" t="s">
         <v>886</v>
       </c>
-      <c r="R5" s="92" t="s">
+      <c r="Z5" s="90" t="s">
         <v>887</v>
       </c>
-      <c r="S5" s="87" t="s">
+      <c r="AA5" s="91" t="s">
         <v>888</v>
       </c>
-      <c r="T5" s="87" t="s">
+      <c r="AB5" s="91" t="s">
         <v>889</v>
       </c>
-      <c r="U5" s="88" t="s">
+      <c r="AC5" s="92" t="s">
         <v>890</v>
       </c>
-      <c r="V5" s="88" t="s">
+      <c r="AD5" s="92" t="s">
         <v>891</v>
       </c>
-      <c r="W5" s="89" t="s">
-        <v>892</v>
-      </c>
-      <c r="X5" s="89" t="s">
-        <v>893</v>
-      </c>
-      <c r="Y5" s="90" t="s">
-        <v>894</v>
-      </c>
-      <c r="Z5" s="90" t="s">
-        <v>895</v>
-      </c>
-      <c r="AA5" s="91" t="s">
-        <v>896</v>
-      </c>
-      <c r="AB5" s="91" t="s">
-        <v>897</v>
-      </c>
-      <c r="AC5" s="92" t="s">
-        <v>898</v>
-      </c>
-      <c r="AD5" s="92" t="s">
-        <v>899</v>
-      </c>
       <c r="AE5" s="30" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AF5" s="31" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AG5" s="32" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
@@ -29585,94 +29591,94 @@
       <c r="B6" s="243"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="G6" s="87">
         <v>1</v>
       </c>
       <c r="H6" s="87" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="I6" s="88">
         <v>2</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="K6" s="89">
         <v>3</v>
       </c>
       <c r="L6" s="89" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="M6" s="90">
         <v>4</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="O6" s="91">
         <v>5</v>
       </c>
       <c r="P6" s="91" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="Q6" s="92">
         <v>6</v>
       </c>
       <c r="R6" s="92" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="S6" s="87">
         <v>7</v>
       </c>
       <c r="T6" s="87" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="U6" s="88">
         <v>8</v>
       </c>
       <c r="V6" s="88" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="W6" s="89">
         <v>9</v>
       </c>
       <c r="X6" s="89" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="Y6" s="90">
         <v>10</v>
       </c>
       <c r="Z6" s="90" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="AA6" s="91">
         <v>11</v>
       </c>
       <c r="AB6" s="91" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="AC6" s="92">
         <v>12</v>
       </c>
       <c r="AD6" s="92" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="AE6" s="93" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AF6" s="94" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AG6" s="95" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AH6" s="96" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="AI6" s="86"/>
     </row>
@@ -29684,94 +29690,94 @@
       <c r="B7" s="243"/>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="G7" s="87" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="H7" s="87" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="I7" s="88" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="J7" s="88" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="L7" s="89" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="M7" s="90" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="O7" s="91" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="P7" s="91" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="Q7" s="92" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="R7" s="92" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="S7" s="87" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="T7" s="87" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="U7" s="88" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="V7" s="88" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="W7" s="89" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="X7" s="89" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="Y7" s="90" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="Z7" s="90" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AA7" s="91" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AB7" s="91" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AC7" s="92" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AD7" s="92" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AE7" s="93" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="AF7" s="94" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="AG7" s="95" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AH7" s="96" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="AI7" s="86"/>
     </row>
@@ -29789,7 +29795,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Hoja_25"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.64453125" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.64453125" style="2" hidden="1" customWidth="1"/>
@@ -29879,7 +29885,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!K24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - SHORT ANSWER
+        <v>FastTest PlugIn - V8.3  - SHORT ANSWER
 Question statement</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -30118,64 +30124,64 @@
         <v>1</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="G5" s="87" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="H5" s="98">
         <v>100</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="J5" s="88" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="K5" s="99">
         <v>100</v>
       </c>
       <c r="L5" s="99" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="M5" s="88" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="N5" s="99">
         <v>100</v>
       </c>
       <c r="O5" s="99" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="P5" s="90" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="Q5" s="100">
         <v>100</v>
       </c>
       <c r="R5" s="100" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="S5" s="91" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="T5" s="101">
         <v>100</v>
       </c>
       <c r="U5" s="101" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="V5" s="92" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="W5" s="102">
         <v>100</v>
       </c>
       <c r="X5" s="102" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="Y5" s="87"/>
       <c r="Z5" s="98"/>
@@ -30184,16 +30190,16 @@
       <c r="AC5" s="99"/>
       <c r="AD5" s="99"/>
       <c r="AE5" s="93" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="AF5" s="94" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="AG5" s="95" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="AH5" s="96" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
@@ -30209,37 +30215,37 @@
         <v>0</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="G6" s="87" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="H6" s="98">
         <v>100</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="K6" s="99">
         <v>50</v>
       </c>
       <c r="L6" s="99" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="M6" s="88" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="N6" s="99">
         <v>100</v>
       </c>
       <c r="O6" s="99" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="P6" s="90"/>
       <c r="Q6" s="100"/>
@@ -30257,10 +30263,10 @@
       <c r="AC6" s="99"/>
       <c r="AD6" s="99"/>
       <c r="AE6" s="93" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="AF6" s="94" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="AG6" s="95"/>
       <c r="AH6" s="96"/>
@@ -30280,7 +30286,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja_26"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -30361,7 +30367,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!M24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - MISSING WORD
+        <v>FastTest PlugIn - V8.3  - MISSING WORD
 Question statement</v>
       </c>
       <c r="G3" s="117" t="str">
@@ -30621,94 +30627,94 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="I5" s="13">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="K5" s="12">
         <v>1</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="M5" s="13">
         <v>1</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="O5" s="12">
         <v>2</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="Q5" s="13">
         <v>2</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="S5" s="12">
         <v>2</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="U5" s="13">
         <v>3</v>
       </c>
       <c r="V5" s="13" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="W5" s="12">
         <v>3</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="Y5" s="13">
         <v>3</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AA5" s="12">
         <v>3</v>
       </c>
       <c r="AB5" s="12" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="AC5" s="13">
         <v>3</v>
       </c>
       <c r="AD5" s="13" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="AE5" s="153" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="AF5" s="154" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="AG5" s="155" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="AH5" s="156" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
@@ -30721,94 +30727,94 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="I6" s="13">
         <v>1</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="K6" s="12">
         <v>1</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="M6" s="13">
         <v>1</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="O6" s="12">
         <v>2</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="Q6" s="13">
         <v>2</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="S6" s="12">
         <v>2</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="U6" s="13">
         <v>3</v>
       </c>
       <c r="V6" s="13" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="W6" s="12">
         <v>3</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="Y6" s="13">
         <v>3</v>
       </c>
       <c r="Z6" s="13" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AA6" s="12">
         <v>3</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="AC6" s="13">
         <v>3</v>
       </c>
       <c r="AD6" s="13" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="AE6" s="153" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="AF6" s="154" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="AG6" s="155" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="AH6" s="156" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="AI6" s="86"/>
     </row>
@@ -30826,7 +30832,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja_27"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -30910,7 +30916,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!O24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - ESSAY
+        <v>FastTest PlugIn - V8.3  - ESSAY
 Question statement</v>
       </c>
       <c r="G3" s="55" t="str">
@@ -31082,29 +31088,29 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="G5" s="128" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="14">
         <v>5</v>
       </c>
       <c r="J5" s="129" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="K5" s="130">
         <v>1</v>
       </c>
       <c r="L5" s="131" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="M5" s="128" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="N5" s="157"/>
       <c r="O5" s="158"/>
@@ -31135,31 +31141,31 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="I6" s="14">
         <v>15</v>
       </c>
       <c r="J6" s="129" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="K6" s="130" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="L6" s="131" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="M6" s="128" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="N6" s="157"/>
       <c r="O6" s="158"/>
@@ -31206,7 +31212,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Hoja_28"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -31273,8 +31279,8 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="276"/>
-      <c r="B3" s="276"/>
+      <c r="A3" s="277"/>
+      <c r="B3" s="277"/>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
       <c r="E3" s="22" t="str">
@@ -31284,7 +31290,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!Q24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - CLOZE
+        <v>FastTest PlugIn - V8.3  - CLOZE
 Question statement</v>
       </c>
       <c r="G3" s="133" t="str">
@@ -31451,10 +31457,10 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="77" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="G5" s="163">
         <v>5</v>
@@ -31496,10 +31502,10 @@
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="77" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="G6" s="163">
         <v>15</v>
@@ -31530,19 +31536,19 @@
       <c r="AC6" s="157"/>
       <c r="AD6" s="157"/>
       <c r="AE6" s="164" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AF6" s="165" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AG6" s="166" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AH6" s="167" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
@@ -31551,10 +31557,10 @@
       <c r="C7" s="152"/>
       <c r="D7" s="152"/>
       <c r="E7" s="77" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="G7" s="163">
         <v>15</v>
